--- a/02_DIA_inicio_2026_analisis_assets/rbd_9705_escuela-basica-salomon-sack_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9705_escuela-basica-salomon-sack_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{030CBDD0-A24C-4112-818A-1C6D1E63F4F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46BEC2CC-D993-482B-AF9B-34F16FE3231E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC3DB49D-40E8-479D-A9EF-5EAFDA25ED7D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D788B8D4-3861-4CE8-BB37-44DDC9DFD7E6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86C26B02-EA52-4836-9ADE-5DC55C9731A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38F6E215-5E82-44D8-9334-62EB220B9084}"/>
 </file>